--- a/data/species_key.xlsx
+++ b/data/species_key.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F085E1A3-5D3B-384A-80DA-F1F955CA5DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18094E9B-4F3B-5C45-9AD9-A745369C045B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7800" yWindow="640" windowWidth="28040" windowHeight="17440" xr2:uid="{59FED1E9-671D-A14E-97CD-E39A7C3D0157}"/>
   </bookViews>
@@ -122,9 +122,6 @@
     <t>Pantropical spotted dolphin</t>
   </si>
   <si>
-    <t>White-beaked dophon</t>
-  </si>
-  <si>
     <t>Atlantic white-sided dolphin</t>
   </si>
   <si>
@@ -468,6 +465,9 @@
   </si>
   <si>
     <t>False killer whale</t>
+  </si>
+  <si>
+    <t>White-beaked dolphin</t>
   </si>
 </sst>
 </file>
@@ -875,7 +875,7 @@
         <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -886,7 +886,7 @@
         <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -897,7 +897,7 @@
         <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -908,7 +908,7 @@
         <v>24</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -916,10 +916,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -927,10 +927,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -938,10 +938,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -949,10 +949,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>27</v>
+        <v>142</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -960,10 +960,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -971,10 +971,10 @@
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -985,7 +985,7 @@
         <v>26</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -996,7 +996,7 @@
         <v>21</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1004,10 +1004,10 @@
         <v>1</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1018,7 +1018,7 @@
         <v>25</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1026,10 +1026,10 @@
         <v>1</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -1037,10 +1037,10 @@
         <v>1</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1048,10 +1048,10 @@
         <v>1</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -1062,7 +1062,7 @@
         <v>8</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -1070,10 +1070,10 @@
         <v>3</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1081,10 +1081,10 @@
         <v>3</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1092,10 +1092,10 @@
         <v>3</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1103,10 +1103,10 @@
         <v>3</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1114,10 +1114,10 @@
         <v>3</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1128,7 +1128,7 @@
         <v>9</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1136,10 +1136,10 @@
         <v>3</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1150,7 +1150,7 @@
         <v>11</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -1161,7 +1161,7 @@
         <v>10</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -1169,10 +1169,10 @@
         <v>3</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1180,10 +1180,10 @@
         <v>3</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -1191,10 +1191,10 @@
         <v>5</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -1202,10 +1202,10 @@
         <v>5</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -1213,10 +1213,10 @@
         <v>5</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1224,10 +1224,10 @@
         <v>5</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -1235,10 +1235,10 @@
         <v>6</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1246,10 +1246,10 @@
         <v>6</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -1257,10 +1257,10 @@
         <v>6</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -1268,10 +1268,10 @@
         <v>6</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -1279,10 +1279,10 @@
         <v>6</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
@@ -1290,10 +1290,10 @@
         <v>6</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
@@ -1301,10 +1301,10 @@
         <v>6</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
@@ -1312,10 +1312,10 @@
         <v>6</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
@@ -1323,10 +1323,10 @@
         <v>6</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
@@ -1334,10 +1334,10 @@
         <v>6</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -1345,10 +1345,10 @@
         <v>2</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
@@ -1356,10 +1356,10 @@
         <v>2</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
@@ -1367,10 +1367,10 @@
         <v>4</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
@@ -1381,7 +1381,7 @@
         <v>13</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
@@ -1392,7 +1392,7 @@
         <v>17</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
@@ -1400,10 +1400,10 @@
         <v>4</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
@@ -1414,7 +1414,7 @@
         <v>20</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -1425,7 +1425,7 @@
         <v>19</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
@@ -1436,7 +1436,7 @@
         <v>18</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
@@ -1444,10 +1444,10 @@
         <v>4</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
@@ -1455,10 +1455,10 @@
         <v>4</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
@@ -1466,10 +1466,10 @@
         <v>4</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
@@ -1480,7 +1480,7 @@
         <v>14</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
@@ -1488,10 +1488,10 @@
         <v>4</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
@@ -1502,7 +1502,7 @@
         <v>12</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
@@ -1513,7 +1513,7 @@
         <v>16</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
@@ -1521,10 +1521,10 @@
         <v>4</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
@@ -1535,7 +1535,7 @@
         <v>15</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
@@ -1543,10 +1543,10 @@
         <v>4</v>
       </c>
       <c r="B62" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
@@ -1554,10 +1554,10 @@
         <v>4</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
@@ -1565,10 +1565,10 @@
         <v>4</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
@@ -1576,10 +1576,10 @@
         <v>4</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
@@ -1587,32 +1587,32 @@
         <v>4</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B67" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B68" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/data/species_key.xlsx
+++ b/data/species_key.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18094E9B-4F3B-5C45-9AD9-A745369C045B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6650E8-D596-F840-AFD1-BAFA63461BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7800" yWindow="640" windowWidth="28040" windowHeight="17440" xr2:uid="{59FED1E9-671D-A14E-97CD-E39A7C3D0157}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$70</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="145">
   <si>
     <t>group</t>
   </si>
@@ -468,13 +468,19 @@
   </si>
   <si>
     <t>White-beaked dolphin</t>
+  </si>
+  <si>
+    <t>Tamanend's bottlenose dolphin</t>
+  </si>
+  <si>
+    <t>Tursiops erebennus</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -497,6 +503,11 @@
       <color rgb="FF040C28"/>
       <name val="Aptos"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -518,11 +529,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -857,17 +869,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC175C07-D47E-6E4A-86F5-247A59810786}">
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -878,7 +890,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -889,7 +901,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -900,7 +912,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -911,7 +923,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
@@ -922,7 +934,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
@@ -933,7 +945,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
@@ -944,7 +956,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
@@ -955,7 +967,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
@@ -966,7 +978,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
@@ -977,7 +989,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
@@ -988,7 +1000,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
@@ -999,7 +1011,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>1</v>
       </c>
@@ -1010,7 +1022,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>1</v>
       </c>
@@ -1021,7 +1033,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>1</v>
       </c>
@@ -1032,7 +1044,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>1</v>
       </c>
@@ -1042,6 +1054,7 @@
       <c r="C16" s="3" t="s">
         <v>67</v>
       </c>
+      <c r="E16" s="4"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
@@ -1056,13 +1069,13 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>8</v>
+        <v>143</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>37</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -1070,10 +1083,10 @@
         <v>3</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1081,10 +1094,10 @@
         <v>3</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>101</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1092,10 +1105,10 @@
         <v>3</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>38</v>
+        <v>115</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1103,10 +1116,10 @@
         <v>3</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>36</v>
+        <v>127</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1114,10 +1127,10 @@
         <v>3</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1125,10 +1138,10 @@
         <v>3</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>9</v>
+        <v>129</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>100</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1136,10 +1149,10 @@
         <v>3</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>130</v>
+        <v>9</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>40</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1147,10 +1160,10 @@
         <v>3</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>11</v>
+        <v>130</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>93</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -1158,10 +1171,10 @@
         <v>3</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>43</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -1169,10 +1182,10 @@
         <v>3</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>131</v>
+        <v>10</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1180,21 +1193,21 @@
         <v>3</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>44</v>
+        <v>131</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>87</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -1202,10 +1215,10 @@
         <v>5</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -1213,10 +1226,10 @@
         <v>5</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1224,21 +1237,21 @@
         <v>5</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>118</v>
+        <v>35</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>82</v>
+        <v>118</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1246,10 +1259,10 @@
         <v>6</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -1257,10 +1270,10 @@
         <v>6</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -1268,10 +1281,10 @@
         <v>6</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -1279,10 +1292,10 @@
         <v>6</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>83</v>
+        <v>30</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
@@ -1290,10 +1303,10 @@
         <v>6</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>81</v>
+        <v>133</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
@@ -1301,10 +1314,10 @@
         <v>6</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>80</v>
+        <v>134</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
@@ -1312,10 +1325,10 @@
         <v>6</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
@@ -1323,10 +1336,10 @@
         <v>6</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>79</v>
+        <v>32</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
@@ -1334,21 +1347,21 @@
         <v>6</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>85</v>
+        <v>119</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>76</v>
+        <v>31</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
@@ -1356,21 +1369,21 @@
         <v>2</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>75</v>
+        <v>135</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>45</v>
+        <v>136</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
@@ -1378,10 +1391,10 @@
         <v>4</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>13</v>
+        <v>137</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
@@ -1389,10 +1402,10 @@
         <v>4</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
@@ -1400,10 +1413,10 @@
         <v>4</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>58</v>
+        <v>17</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
@@ -1411,10 +1424,10 @@
         <v>4</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>57</v>
+        <v>109</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -1422,10 +1435,10 @@
         <v>4</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
@@ -1433,10 +1446,10 @@
         <v>4</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
@@ -1444,10 +1457,10 @@
         <v>4</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>92</v>
+        <v>18</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
@@ -1455,10 +1468,10 @@
         <v>4</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>59</v>
+        <v>124</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
@@ -1466,10 +1479,10 @@
         <v>4</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>99</v>
+        <v>138</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
@@ -1477,10 +1490,10 @@
         <v>4</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>14</v>
+        <v>120</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
@@ -1488,10 +1501,10 @@
         <v>4</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>121</v>
+        <v>14</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
@@ -1499,10 +1512,10 @@
         <v>4</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>12</v>
+        <v>121</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
@@ -1510,10 +1523,10 @@
         <v>4</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
@@ -1521,10 +1534,10 @@
         <v>4</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>49</v>
+        <v>16</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
@@ -1532,10 +1545,10 @@
         <v>4</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>97</v>
+        <v>139</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
@@ -1543,10 +1556,10 @@
         <v>4</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>96</v>
+        <v>15</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
@@ -1554,10 +1567,10 @@
         <v>4</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
@@ -1565,10 +1578,10 @@
         <v>4</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>54</v>
+        <v>122</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
@@ -1576,10 +1589,10 @@
         <v>4</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
@@ -1587,21 +1600,21 @@
         <v>4</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>106</v>
+        <v>4</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>103</v>
+        <v>47</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
@@ -1609,16 +1622,27 @@
         <v>106</v>
       </c>
       <c r="B68" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C69" s="1" t="s">
         <v>105</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C69" xr:uid="{BC175C07-D47E-6E4A-86F5-247A59810786}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C68">
-      <sortCondition ref="A1:A69"/>
+  <autoFilter ref="A1:C70" xr:uid="{BC175C07-D47E-6E4A-86F5-247A59810786}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C69">
+      <sortCondition ref="A1:A70"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/species_key.xlsx
+++ b/data/species_key.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6650E8-D596-F840-AFD1-BAFA63461BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C306D098-41E6-A14B-B7BB-A9F135ED6978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7800" yWindow="640" windowWidth="28040" windowHeight="17440" xr2:uid="{59FED1E9-671D-A14E-97CD-E39A7C3D0157}"/>
+    <workbookView xWindow="44400" yWindow="3860" windowWidth="28040" windowHeight="17440" xr2:uid="{59FED1E9-671D-A14E-97CD-E39A7C3D0157}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$72</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="160">
   <si>
     <t>group</t>
   </si>
@@ -474,6 +474,51 @@
   </si>
   <si>
     <t>Tursiops erebennus</t>
+  </si>
+  <si>
+    <t>Pacific walrus</t>
+  </si>
+  <si>
+    <t>Polar bear</t>
+  </si>
+  <si>
+    <t>West Indian manatee</t>
+  </si>
+  <si>
+    <t>Odobenus rosmarus</t>
+  </si>
+  <si>
+    <t>Ursus maritimus</t>
+  </si>
+  <si>
+    <t>Trichechus manatus</t>
+  </si>
+  <si>
+    <t>Ginkgo-toothed beaked whale</t>
+  </si>
+  <si>
+    <t>Mesoplodon ginkgodens</t>
+  </si>
+  <si>
+    <t>Antarctic fur seal</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Arctocephalus gazella</t>
+  </si>
+  <si>
+    <t>Indo-Pacific bottlenose dolphin</t>
+  </si>
+  <si>
+    <t>Tursiops aduncus</t>
+  </si>
+  <si>
+    <t>Pygmy/dwarf sperm whale</t>
+  </si>
+  <si>
+    <t>Kogia spp.</t>
   </si>
 </sst>
 </file>
@@ -869,7 +914,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC175C07-D47E-6E4A-86F5-247A59810786}">
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.1640625" style="1" bestFit="1" customWidth="1"/>
@@ -1639,12 +1684,85 @@
         <v>105</v>
       </c>
     </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B72" t="s">
+        <v>147</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C70" xr:uid="{BC175C07-D47E-6E4A-86F5-247A59810786}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C69">
-      <sortCondition ref="A1:A70"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:C72" xr:uid="{BC175C07-D47E-6E4A-86F5-247A59810786}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>